--- a/chapters/02/core/AIHE-A04/supp/AIHE-U/xlsx/AIHE-U_workbook.xlsx
+++ b/chapters/02/core/AIHE-A04/supp/AIHE-U/xlsx/AIHE-U_workbook.xlsx
@@ -80,7 +80,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -88,7 +88,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,10 +118,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,10 +129,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
